--- a/sim_data.xlsx
+++ b/sim_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,78 +429,3474 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>sim_ticks</t>
+          <t>sim_insts</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>host_mem_usage</t>
+          <t>system.cpu.numCycles</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>system.cpu.ipc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>host_seconds</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>system.cpu.dcache.overall_miss_rate::total</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>system.cpu.icache.overall_miss_rate::total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>system.l2cache.overall_misses::total</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>system.l3cache.overall_miss_rate::total</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>system.cpu.commit.branches</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>system.cpu.branchPred.condPredicted</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>system.cpu.branchPred.condIncorrect</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test1.txt</t>
+          <t>convolution_config1_b.txt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.000044</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44318000</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>659648</t>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>935</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>test2.txt</t>
+          <t>mergesort_config1_b.txt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.000044</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44318000</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>659648</t>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stats.txt</t>
+          <t>mergesort_config1_c.txt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.000044</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>44318000</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>659648</t>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>convolution_config1_c.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mergesort_config3_a.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>convolution_config3_a.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>convolution_config3_c.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mergesort_config3_c.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>convolution_config1_a.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mergesort_config1_a.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mergesort_fixed.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mergesort_config3_b.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>convolution_config3_b.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>convolution_config5_a.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mergesort_config5_a.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mergesort_config5_c.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>convolution_config5_c.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>convolution_config5_b.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mergesort_config5_b.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>convolution_config2_c.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mergesort_config2_c.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mergesort_config2_b.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>convolution_config2_b.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mergesort_config2_a.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>convolution_config2_a.txt</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bfs_base.txt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.000047</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>94322</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.082070</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.105032</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.268511</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mergesort_config4_c.txt</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>convolution_config4_c.txt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>convolution_config4_b.txt</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mergesort_config4_b.txt</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mergesort_base.txt</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.000046</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>91653</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.084198</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.104794</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.244786</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>convolution_config4_a.txt</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mergesort_config4_a.txt</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7717</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>86932</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.088771</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.095070</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.200116</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>convolution_fixed.txt</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>85663</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.090342</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.094995</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.199706</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bfs_config2_a.txt</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bfs_config2_c.txt</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bfs_config2_b.txt</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bfs_config4_a.txt</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>bfs_config4_c.txt</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bfs_config4_b.txt</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bfs_config3_c.txt</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bfs_config1_a.txt</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bfs_config3_b.txt</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bfs_config1_b.txt</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bfs_config1_c.txt</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bfs_config3_a.txt</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bfs_config5_c.txt</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>convolution_base.txt</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0.000046</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>91194</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.084863</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.102621</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.249303</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bfs_config5_b.txt</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bfs_fixed.txt</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bfs_config5_a.txt</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0.000045</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.086885</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.096324</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.216085</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>941</t>
         </is>
       </c>
     </row>

--- a/sim_data.xlsx
+++ b/sim_data.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,32 +501,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,32 +568,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,32 +635,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,32 +702,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,32 +769,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -836,32 +836,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -903,32 +903,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -970,32 +970,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1037,32 +1037,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1104,32 +1104,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1171,32 +1171,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1238,32 +1238,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1305,32 +1305,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1372,32 +1372,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1439,32 +1439,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1506,32 +1506,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1573,32 +1573,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1640,32 +1640,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1841,32 +1841,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1908,32 +1908,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1975,32 +1975,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2109,32 +2109,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2243,32 +2243,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2444,32 +2444,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2578,32 +2578,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2645,32 +2645,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>86932</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.088771</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.095070</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.200116</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>0.000046</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2712,32 +2712,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>85663</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.090342</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.094995</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.199706</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2779,32 +2779,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2846,32 +2846,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2913,32 +2913,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2980,32 +2980,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3047,32 +3047,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3181,32 +3181,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3248,32 +3248,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3315,32 +3315,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3382,32 +3382,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3516,32 +3516,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3583,32 +3583,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3650,32 +3650,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>91194</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.084863</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.102621</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.249303</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>854</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3717,32 +3717,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3784,32 +3784,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0.000045</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3851,32 +3851,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.086885</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.096324</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.216085</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>864</t>
         </is>
       </c>
     </row>

--- a/sim_data.xlsx
+++ b/sim_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,42 +491,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000716</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>973299</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>1431063</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.680123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.001526</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.006359</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -536,17 +536,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>169835</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>5554</t>
         </is>
       </c>
     </row>
@@ -558,42 +558,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000252</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>298818</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>503152</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.593892</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.003366</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.017098</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>57499</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>5181</t>
         </is>
       </c>
     </row>
@@ -625,42 +625,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000252</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>298818</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>503152</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.593892</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.003366</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.017098</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -670,17 +670,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>57499</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>5181</t>
         </is>
       </c>
     </row>
@@ -692,42 +692,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000716</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>973299</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>1431063</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.680123</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.001526</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.006359</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>169835</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>5554</t>
         </is>
       </c>
     </row>
@@ -1027,42 +1027,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000716</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>973299</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>1431063</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.680123</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.001526</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.006359</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1072,17 +1072,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>169835</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>5554</t>
         </is>
       </c>
     </row>
@@ -1094,42 +1094,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000252</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>298818</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>503152</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.593892</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.003366</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.017098</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>57499</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>5181</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000044</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1171,32 +1171,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>87352</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.088344</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.096370</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.206244</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>799</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>945</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>convolution_config5_a.txt</t>
+          <t>convolution_config2_c.txt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mergesort_config5_a.txt</t>
+          <t>mergesort_config2_c.txt</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1491,7 +1491,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mergesort_config5_c.txt</t>
+          <t>mergesort_config2_b.txt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>convolution_config5_c.txt</t>
+          <t>convolution_config2_b.txt</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>convolution_config5_b.txt</t>
+          <t>mergesort_config2_a.txt</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1635,37 +1635,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.084198</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.104794</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.244786</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>861</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mergesort_config5_b.txt</t>
+          <t>convolution_config2_a.txt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1702,17 +1702,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.084853</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.103073</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.247129</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1742,64 +1742,64 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>854</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>convolution_config2_c.txt</t>
+          <t>bfs_base.txt</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000345</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>472405</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>689746</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.684897</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.003766</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.012426</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1809,64 +1809,64 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>4481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mergesort_config2_c.txt</t>
+          <t>mergesort_base.txt</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000252</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>298818</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>503152</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.593892</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.003366</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.017098</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1876,64 +1876,64 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>57499</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>5181</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mergesort_config2_b.txt</t>
+          <t>convolution_fixed.txt</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>86920</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.089036</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.094096</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.205496</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>790</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1943,44 +1943,44 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>943</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>convolution_config2_b.txt</t>
+          <t>bfs_config2_a.txt</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2010,64 +2010,64 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>864</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mergesort_config2_a.txt</t>
+          <t>bfs_config2_c.txt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2077,64 +2077,64 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>864</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>convolution_config2_a.txt</t>
+          <t>bfs_config2_b.txt</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2144,24 +2144,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>864</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bfs_base.txt</t>
+          <t>bfs_config3_c.txt</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2228,47 +2228,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mergesort_config4_c.txt</t>
+          <t>bfs_config1_a.txt</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000345</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>472405</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>689746</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.684897</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.003766</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.012426</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2278,64 +2278,64 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>4481</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>convolution_config4_c.txt</t>
+          <t>bfs_config3_b.txt</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2345,64 +2345,64 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>864</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>convolution_config4_b.txt</t>
+          <t>bfs_config1_b.txt</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000345</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>472405</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>689746</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.684897</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.003766</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.012426</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2412,64 +2412,64 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>4481</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mergesort_config4_b.txt</t>
+          <t>bfs_config1_c.txt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>472405</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>689746</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.684897</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.003766</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.012426</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2479,64 +2479,64 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>4481</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mergesort_base.txt</t>
+          <t>bfs_config3_a.txt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000047</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.082070</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.105032</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.268511</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>776</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2546,64 +2546,64 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>864</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>convolution_config4_a.txt</t>
+          <t>convolution_base.txt</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000716</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>973299</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>1431063</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.680123</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.103073</t>
+          <t>0.001526</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.247129</t>
+          <t>0.006359</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2613,64 +2613,64 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>169835</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>5554</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mergesort_config4_a.txt</t>
+          <t>bfs_fixed.txt</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.000045</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>89327</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.086659</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.104794</t>
+          <t>0.096095</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.244786</t>
+          <t>0.221632</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>812</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2680,1223 +2680,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>861</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>convolution_fixed.txt</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0.000046</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7739</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>91205</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.084853</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.103073</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.247129</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>1585</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>bfs_config2_a.txt</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>bfs_config2_c.txt</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>bfs_config2_b.txt</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>bfs_config4_a.txt</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>bfs_config4_c.txt</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>bfs_config4_b.txt</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>bfs_config3_c.txt</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>bfs_config1_a.txt</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>bfs_config3_b.txt</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>bfs_config1_b.txt</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>bfs_config1_c.txt</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>bfs_config3_a.txt</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>bfs_config5_c.txt</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>convolution_base.txt</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>0.000046</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7739</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>91205</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0.084853</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0.103073</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>0.247129</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>1585</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>bfs_config5_b.txt</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>bfs_fixed.txt</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>bfs_config5_a.txt</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>0.000047</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.082070</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0.105032</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>0.268511</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>3846</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>864</t>
+          <t>932</t>
         </is>
       </c>
     </row>

--- a/sim_data.xlsx
+++ b/sim_data.xlsx
@@ -662,12 +662,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.036272</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.861913</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.010476</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.899004</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.011035</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.853461</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.037789</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.827302</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.013619</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.084198</t>
+          <t>0.691527</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.000046</t>
+          <t>0.045749</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.084853</t>
+          <t>0.683356</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.000047</t>
+          <t>0.060812</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.082070</t>
+          <t>0.699877</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.000047</t>
+          <t>0.043844</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.082070</t>
+          <t>0.970726</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.000047</t>
+          <t>0.047083</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.082070</t>
+          <t>0.903962</t>
         </is>
       </c>
     </row>
